--- a/data/source-workbooks/driver_templates_expanded.xlsx
+++ b/data/source-workbooks/driver_templates_expanded.xlsx
@@ -503,112 +503,112 @@
     <t>Robert Johnson</t>
   </si>
   <si>
-    <t>1240 W 6th St, Cleveland, OH 44113</t>
-  </si>
-  <si>
-    <t>450 N Michigan Ave, Chicago, IL 60611</t>
-  </si>
-  <si>
-    <t>780 Peachtree St, Atlanta, GA 30308</t>
-  </si>
-  <si>
-    <t>2200 Superior Ave, Cleveland, OH 44114</t>
-  </si>
-  <si>
-    <t>115 E Broad St, Columbus, OH 43215</t>
-  </si>
-  <si>
-    <t>500 Pacific Ave, Dallas, TX 75202</t>
-  </si>
-  <si>
-    <t>815 Prospect Ave, Cleveland, OH 44115</t>
-  </si>
-  <si>
-    <t>240 Madison Ave, Toledo, OH 43604</t>
-  </si>
-  <si>
-    <t>330 Civic Center Dr, Columbus, OH 43215</t>
-  </si>
-  <si>
-    <t>110 W Adams St, Chicago, IL 60603</t>
-  </si>
-  <si>
-    <t>600 Peachtree St, Atlanta, GA 30308</t>
-  </si>
-  <si>
-    <t>618 S Michigan Ave, Chicago, IL 60605</t>
-  </si>
-  <si>
-    <t>206-667-3424</t>
-  </si>
-  <si>
-    <t>707-773-6386</t>
-  </si>
-  <si>
-    <t>675-486-1335</t>
-  </si>
-  <si>
-    <t>359-469-5960</t>
-  </si>
-  <si>
-    <t>871-429-6220</t>
-  </si>
-  <si>
-    <t>283-876-4322</t>
-  </si>
-  <si>
-    <t>896-828-7164</t>
-  </si>
-  <si>
-    <t>820-223-4829</t>
-  </si>
-  <si>
-    <t>206-700-7666</t>
-  </si>
-  <si>
-    <t>582-987-2387</t>
-  </si>
-  <si>
-    <t>337-857-3607</t>
-  </si>
-  <si>
-    <t>618-667-2121</t>
-  </si>
-  <si>
-    <t>***-**-9443</t>
-  </si>
-  <si>
-    <t>***-**-3407</t>
-  </si>
-  <si>
-    <t>***-**-7047</t>
-  </si>
-  <si>
-    <t>***-**-8257</t>
-  </si>
-  <si>
-    <t>***-**-1789</t>
-  </si>
-  <si>
-    <t>***-**-1521</t>
-  </si>
-  <si>
-    <t>***-**-4815</t>
-  </si>
-  <si>
-    <t>***-**-4800</t>
-  </si>
-  <si>
-    <t>***-**-9930</t>
-  </si>
-  <si>
-    <t>***-**-5590</t>
-  </si>
-  <si>
-    <t>***-**-5273</t>
-  </si>
-  <si>
-    <t>***-**-5664</t>
+    <t>220 Demo Street, Cleveland, OH 44113</t>
+  </si>
+  <si>
+    <t>770 Demo Street, Chicago, IL 60611</t>
+  </si>
+  <si>
+    <t>960 Demo Street, Atlanta, GA 30308</t>
+  </si>
+  <si>
+    <t>520 Demo Street, Cleveland, OH 44114</t>
+  </si>
+  <si>
+    <t>150 Demo Street, Columbus, OH 43215</t>
+  </si>
+  <si>
+    <t>810 Demo Street, Dallas, TX 75202</t>
+  </si>
+  <si>
+    <t>1020 Demo Street, Cleveland, OH 44115</t>
+  </si>
+  <si>
+    <t>530 Demo Street, Toledo, OH 43604</t>
+  </si>
+  <si>
+    <t>630 Demo Street, Columbus, OH 43215</t>
+  </si>
+  <si>
+    <t>130 Demo Street, Chicago, IL 60603</t>
+  </si>
+  <si>
+    <t>900 Demo Street, Atlanta, GA 30308</t>
+  </si>
+  <si>
+    <t>920 Demo Street, Chicago, IL 60605</t>
+  </si>
+  <si>
+    <t>206-555-0102</t>
+  </si>
+  <si>
+    <t>707-555-0100</t>
+  </si>
+  <si>
+    <t>675-555-0100</t>
+  </si>
+  <si>
+    <t>359-555-0100</t>
+  </si>
+  <si>
+    <t>871-555-0100</t>
+  </si>
+  <si>
+    <t>283-555-0100</t>
+  </si>
+  <si>
+    <t>896-555-0100</t>
+  </si>
+  <si>
+    <t>820-555-0100</t>
+  </si>
+  <si>
+    <t>206-555-0103</t>
+  </si>
+  <si>
+    <t>582-555-0100</t>
+  </si>
+  <si>
+    <t>337-555-0100</t>
+  </si>
+  <si>
+    <t>618-555-0101</t>
+  </si>
+  <si>
+    <t>***-**-0123</t>
+  </si>
+  <si>
+    <t>***-**-0105</t>
+  </si>
+  <si>
+    <t>***-**-0116</t>
+  </si>
+  <si>
+    <t>***-**-0119</t>
+  </si>
+  <si>
+    <t>***-**-0102</t>
+  </si>
+  <si>
+    <t>***-**-0101</t>
+  </si>
+  <si>
+    <t>***-**-0109</t>
+  </si>
+  <si>
+    <t>***-**-0108</t>
+  </si>
+  <si>
+    <t>***-**-0124</t>
+  </si>
+  <si>
+    <t>***-**-0112</t>
+  </si>
+  <si>
+    <t>***-**-0111</t>
+  </si>
+  <si>
+    <t>***-**-0114</t>
   </si>
   <si>
     <t>Huntington</t>
@@ -653,256 +653,256 @@
     <t>VALID</t>
   </si>
   <si>
-    <t>OH1668243</t>
-  </si>
-  <si>
-    <t>OH2933152</t>
-  </si>
-  <si>
-    <t>OH6381314</t>
-  </si>
-  <si>
-    <t>OH8275310</t>
-  </si>
-  <si>
-    <t>OH8643525</t>
-  </si>
-  <si>
-    <t>OH8694835</t>
-  </si>
-  <si>
-    <t>OH7359899</t>
-  </si>
-  <si>
-    <t>IL3091126</t>
-  </si>
-  <si>
-    <t>IL9530000</t>
-  </si>
-  <si>
-    <t>IL3900948</t>
-  </si>
-  <si>
-    <t>IL6663817</t>
-  </si>
-  <si>
-    <t>IL9293900</t>
-  </si>
-  <si>
-    <t>IL4346440</t>
-  </si>
-  <si>
-    <t>IL4913140</t>
-  </si>
-  <si>
-    <t>GA7446431</t>
-  </si>
-  <si>
-    <t>GA3549920</t>
-  </si>
-  <si>
-    <t>GA5957495</t>
-  </si>
-  <si>
-    <t>GA3499514</t>
-  </si>
-  <si>
-    <t>GA3381500</t>
-  </si>
-  <si>
-    <t>GA8768417</t>
-  </si>
-  <si>
-    <t>GA1828575</t>
-  </si>
-  <si>
-    <t>OH8493496</t>
-  </si>
-  <si>
-    <t>OH4694295</t>
-  </si>
-  <si>
-    <t>OH7280038</t>
-  </si>
-  <si>
-    <t>OH9775880</t>
-  </si>
-  <si>
-    <t>OH1046362</t>
-  </si>
-  <si>
-    <t>OH1138650</t>
-  </si>
-  <si>
-    <t>OH4059570</t>
-  </si>
-  <si>
-    <t>OH2779041</t>
-  </si>
-  <si>
-    <t>OH3434069</t>
-  </si>
-  <si>
-    <t>OH6720716</t>
-  </si>
-  <si>
-    <t>OH5640312</t>
-  </si>
-  <si>
-    <t>OH7627072</t>
-  </si>
-  <si>
-    <t>OH1919210</t>
-  </si>
-  <si>
-    <t>OH7765263</t>
-  </si>
-  <si>
-    <t>TX3261112</t>
-  </si>
-  <si>
-    <t>TX3531641</t>
-  </si>
-  <si>
-    <t>TX2647879</t>
-  </si>
-  <si>
-    <t>TX3779357</t>
-  </si>
-  <si>
-    <t>TX3175879</t>
-  </si>
-  <si>
-    <t>TX8659153</t>
-  </si>
-  <si>
-    <t>TX3212501</t>
-  </si>
-  <si>
-    <t>OH6635833</t>
-  </si>
-  <si>
-    <t>OH6094308</t>
-  </si>
-  <si>
-    <t>OH5247055</t>
-  </si>
-  <si>
-    <t>OH8453480</t>
-  </si>
-  <si>
-    <t>OH6843221</t>
-  </si>
-  <si>
-    <t>OH6877493</t>
-  </si>
-  <si>
-    <t>OH1110710</t>
-  </si>
-  <si>
-    <t>OH9450480</t>
-  </si>
-  <si>
-    <t>OH8889985</t>
-  </si>
-  <si>
-    <t>OH2899009</t>
-  </si>
-  <si>
-    <t>OH8294998</t>
-  </si>
-  <si>
-    <t>OH3539286</t>
-  </si>
-  <si>
-    <t>OH4520738</t>
-  </si>
-  <si>
-    <t>OH9851872</t>
-  </si>
-  <si>
-    <t>OH6116714</t>
-  </si>
-  <si>
-    <t>OH2742151</t>
-  </si>
-  <si>
-    <t>OH5031927</t>
-  </si>
-  <si>
-    <t>OH9570143</t>
-  </si>
-  <si>
-    <t>OH7265424</t>
-  </si>
-  <si>
-    <t>OH4179820</t>
-  </si>
-  <si>
-    <t>OH9306784</t>
-  </si>
-  <si>
-    <t>IL3858215</t>
-  </si>
-  <si>
-    <t>IL2016981</t>
-  </si>
-  <si>
-    <t>IL4814730</t>
-  </si>
-  <si>
-    <t>IL4355788</t>
-  </si>
-  <si>
-    <t>IL6567205</t>
-  </si>
-  <si>
-    <t>IL6135045</t>
-  </si>
-  <si>
-    <t>IL2535912</t>
-  </si>
-  <si>
-    <t>GA8190601</t>
-  </si>
-  <si>
-    <t>GA4750278</t>
-  </si>
-  <si>
-    <t>GA5818610</t>
-  </si>
-  <si>
-    <t>GA5852321</t>
-  </si>
-  <si>
-    <t>GA6447082</t>
-  </si>
-  <si>
-    <t>GA5384195</t>
-  </si>
-  <si>
-    <t>GA1861689</t>
-  </si>
-  <si>
-    <t>IL1895570</t>
-  </si>
-  <si>
-    <t>IL5451183</t>
-  </si>
-  <si>
-    <t>IL2852329</t>
-  </si>
-  <si>
-    <t>IL4305571</t>
-  </si>
-  <si>
-    <t>IL8325086</t>
-  </si>
-  <si>
-    <t>IL3423206</t>
-  </si>
-  <si>
-    <t>IL2655126</t>
+    <t>OH0000075</t>
+  </si>
+  <si>
+    <t>OH0000092</t>
+  </si>
+  <si>
+    <t>OH0000111</t>
+  </si>
+  <si>
+    <t>OH0000127</t>
+  </si>
+  <si>
+    <t>OH0000137</t>
+  </si>
+  <si>
+    <t>OH0000138</t>
+  </si>
+  <si>
+    <t>OH0000124</t>
+  </si>
+  <si>
+    <t>IL0000041</t>
+  </si>
+  <si>
+    <t>IL0000068</t>
+  </si>
+  <si>
+    <t>IL0000056</t>
+  </si>
+  <si>
+    <t>IL0000065</t>
+  </si>
+  <si>
+    <t>IL0000067</t>
+  </si>
+  <si>
+    <t>IL0000058</t>
+  </si>
+  <si>
+    <t>IL0000061</t>
+  </si>
+  <si>
+    <t>GA0000013</t>
+  </si>
+  <si>
+    <t>GA0000006</t>
+  </si>
+  <si>
+    <t>GA0000011</t>
+  </si>
+  <si>
+    <t>GA0000005</t>
+  </si>
+  <si>
+    <t>GA0000004</t>
+  </si>
+  <si>
+    <t>GA0000027</t>
+  </si>
+  <si>
+    <t>GA0000002</t>
+  </si>
+  <si>
+    <t>OH0000130</t>
+  </si>
+  <si>
+    <t>OH0000099</t>
+  </si>
+  <si>
+    <t>OH0000123</t>
+  </si>
+  <si>
+    <t>OH0000149</t>
+  </si>
+  <si>
+    <t>OH0000072</t>
+  </si>
+  <si>
+    <t>OH0000074</t>
+  </si>
+  <si>
+    <t>OH0000095</t>
+  </si>
+  <si>
+    <t>OH0000084</t>
+  </si>
+  <si>
+    <t>OH0000093</t>
+  </si>
+  <si>
+    <t>OH0000119</t>
+  </si>
+  <si>
+    <t>OH0000102</t>
+  </si>
+  <si>
+    <t>OH0000125</t>
+  </si>
+  <si>
+    <t>OH0000082</t>
+  </si>
+  <si>
+    <t>OH0000126</t>
+  </si>
+  <si>
+    <t>TX0000158</t>
+  </si>
+  <si>
+    <t>TX0000165</t>
+  </si>
+  <si>
+    <t>TX0000155</t>
+  </si>
+  <si>
+    <t>TX0000166</t>
+  </si>
+  <si>
+    <t>TX0000156</t>
+  </si>
+  <si>
+    <t>TX0000167</t>
+  </si>
+  <si>
+    <t>TX0000157</t>
+  </si>
+  <si>
+    <t>OH0000112</t>
+  </si>
+  <si>
+    <t>OH0000103</t>
+  </si>
+  <si>
+    <t>OH0000101</t>
+  </si>
+  <si>
+    <t>OH0000129</t>
+  </si>
+  <si>
+    <t>OH0000120</t>
+  </si>
+  <si>
+    <t>OH0000121</t>
+  </si>
+  <si>
+    <t>OH0000073</t>
+  </si>
+  <si>
+    <t>OH0000141</t>
+  </si>
+  <si>
+    <t>OH0000139</t>
+  </si>
+  <si>
+    <t>OH0000091</t>
+  </si>
+  <si>
+    <t>OH0000128</t>
+  </si>
+  <si>
+    <t>OH0000094</t>
+  </si>
+  <si>
+    <t>OH0000098</t>
+  </si>
+  <si>
+    <t>OH0000150</t>
+  </si>
+  <si>
+    <t>OH0000104</t>
+  </si>
+  <si>
+    <t>OH0000083</t>
+  </si>
+  <si>
+    <t>OH0000100</t>
+  </si>
+  <si>
+    <t>OH0000148</t>
+  </si>
+  <si>
+    <t>OH0000122</t>
+  </si>
+  <si>
+    <t>OH0000096</t>
+  </si>
+  <si>
+    <t>OH0000140</t>
+  </si>
+  <si>
+    <t>IL0000049</t>
+  </si>
+  <si>
+    <t>IL0000037</t>
+  </si>
+  <si>
+    <t>IL0000060</t>
+  </si>
+  <si>
+    <t>IL0000059</t>
+  </si>
+  <si>
+    <t>IL0000064</t>
+  </si>
+  <si>
+    <t>IL0000063</t>
+  </si>
+  <si>
+    <t>IL0000038</t>
+  </si>
+  <si>
+    <t>GA0000020</t>
+  </si>
+  <si>
+    <t>GA0000007</t>
+  </si>
+  <si>
+    <t>GA0000009</t>
+  </si>
+  <si>
+    <t>GA0000010</t>
+  </si>
+  <si>
+    <t>GA0000012</t>
+  </si>
+  <si>
+    <t>GA0000008</t>
+  </si>
+  <si>
+    <t>GA0000003</t>
+  </si>
+  <si>
+    <t>IL0000030</t>
+  </si>
+  <si>
+    <t>IL0000062</t>
+  </si>
+  <si>
+    <t>IL0000040</t>
+  </si>
+  <si>
+    <t>IL0000057</t>
+  </si>
+  <si>
+    <t>IL0000066</t>
+  </si>
+  <si>
+    <t>IL0000048</t>
+  </si>
+  <si>
+    <t>IL0000039</t>
   </si>
   <si>
     <t>Load L-501: Seal mismatch detected. Pickup: SEAL-83921 Delivery: SEAL-83920.</t>
@@ -1019,76 +1019,76 @@
     <t>South Asian</t>
   </si>
   <si>
-    <t>jcarter@yahoo.com</t>
-  </si>
-  <si>
-    <t>marialopez@aol.com</t>
-  </si>
-  <si>
-    <t>alexkim@gmail.com</t>
-  </si>
-  <si>
-    <t>priyapatel@yahoo.com</t>
-  </si>
-  <si>
-    <t>ktanaka@yahoo.com</t>
-  </si>
-  <si>
-    <t>mchen@hotmail.com</t>
-  </si>
-  <si>
-    <t>sofiagomez@yahoo.com</t>
-  </si>
-  <si>
-    <t>liamsmith@gmail.com</t>
-  </si>
-  <si>
-    <t>emmabrown@yahoo.com</t>
-  </si>
-  <si>
-    <t>nwilson@gmail.com</t>
-  </si>
-  <si>
-    <t>olee@hotmail.com</t>
-  </si>
-  <si>
-    <t>robertjohnson@hotmail.com</t>
-  </si>
-  <si>
-    <t>1240 W 6th St</t>
-  </si>
-  <si>
-    <t>450 N Michigan Ave</t>
-  </si>
-  <si>
-    <t>780 Peachtree St</t>
-  </si>
-  <si>
-    <t>2200 Superior Ave</t>
-  </si>
-  <si>
-    <t>115 E Broad St</t>
-  </si>
-  <si>
-    <t>500 Pacific Ave</t>
-  </si>
-  <si>
-    <t>815 Prospect Ave</t>
-  </si>
-  <si>
-    <t>240 Madison Ave</t>
-  </si>
-  <si>
-    <t>330 Civic Center Dr</t>
-  </si>
-  <si>
-    <t>110 W Adams St</t>
-  </si>
-  <si>
-    <t>600 Peachtree St</t>
-  </si>
-  <si>
-    <t>618 S Michigan Ave</t>
+    <t>jcarter@example.com</t>
+  </si>
+  <si>
+    <t>marialopez@example.com</t>
+  </si>
+  <si>
+    <t>alexkim@example.com</t>
+  </si>
+  <si>
+    <t>priyapatel@example.com</t>
+  </si>
+  <si>
+    <t>ktanaka@example.com</t>
+  </si>
+  <si>
+    <t>mchen@example.com</t>
+  </si>
+  <si>
+    <t>sofiagomez@example.com</t>
+  </si>
+  <si>
+    <t>liamsmith@example.com</t>
+  </si>
+  <si>
+    <t>emmabrown@example.com</t>
+  </si>
+  <si>
+    <t>nwilson@example.com</t>
+  </si>
+  <si>
+    <t>olee@example.com</t>
+  </si>
+  <si>
+    <t>robertjohnson@example.com</t>
+  </si>
+  <si>
+    <t>220 Demo Street</t>
+  </si>
+  <si>
+    <t>770 Demo Street</t>
+  </si>
+  <si>
+    <t>960 Demo Street</t>
+  </si>
+  <si>
+    <t>520 Demo Street</t>
+  </si>
+  <si>
+    <t>150 Demo Street</t>
+  </si>
+  <si>
+    <t>810 Demo Street</t>
+  </si>
+  <si>
+    <t>1020 Demo Street</t>
+  </si>
+  <si>
+    <t>530 Demo Street</t>
+  </si>
+  <si>
+    <t>630 Demo Street</t>
+  </si>
+  <si>
+    <t>130 Demo Street</t>
+  </si>
+  <si>
+    <t>900 Demo Street</t>
+  </si>
+  <si>
+    <t>920 Demo Street</t>
   </si>
   <si>
     <t>Cleveland</t>
@@ -1484,259 +1484,259 @@
     <t>Johnson</t>
   </si>
   <si>
-    <t>OH1668244</t>
-  </si>
-  <si>
-    <t>OH1668245</t>
-  </si>
-  <si>
-    <t>OH1668246</t>
-  </si>
-  <si>
-    <t>OH1668247</t>
-  </si>
-  <si>
-    <t>OH1668248</t>
-  </si>
-  <si>
-    <t>OH1668249</t>
-  </si>
-  <si>
-    <t>IL3091127</t>
-  </si>
-  <si>
-    <t>IL3091128</t>
-  </si>
-  <si>
-    <t>IL3091129</t>
-  </si>
-  <si>
-    <t>IL3091130</t>
-  </si>
-  <si>
-    <t>IL3091131</t>
-  </si>
-  <si>
-    <t>IL3091132</t>
-  </si>
-  <si>
-    <t>GA7446432</t>
-  </si>
-  <si>
-    <t>GA7446433</t>
-  </si>
-  <si>
-    <t>GA7446434</t>
-  </si>
-  <si>
-    <t>GA7446435</t>
-  </si>
-  <si>
-    <t>GA7446436</t>
-  </si>
-  <si>
-    <t>GA7446437</t>
-  </si>
-  <si>
-    <t>OH8493497</t>
-  </si>
-  <si>
-    <t>OH8493498</t>
-  </si>
-  <si>
-    <t>OH8493499</t>
-  </si>
-  <si>
-    <t>OH8493500</t>
-  </si>
-  <si>
-    <t>OH8493501</t>
-  </si>
-  <si>
-    <t>OH8493502</t>
-  </si>
-  <si>
-    <t>OH2779042</t>
-  </si>
-  <si>
-    <t>OH2779043</t>
-  </si>
-  <si>
-    <t>OH2779044</t>
-  </si>
-  <si>
-    <t>OH2779045</t>
-  </si>
-  <si>
-    <t>OH2779046</t>
-  </si>
-  <si>
-    <t>OH2779047</t>
-  </si>
-  <si>
-    <t>TX3261113</t>
-  </si>
-  <si>
-    <t>TX3261114</t>
-  </si>
-  <si>
-    <t>TX3261115</t>
-  </si>
-  <si>
-    <t>TX3261116</t>
-  </si>
-  <si>
-    <t>TX3261117</t>
-  </si>
-  <si>
-    <t>TX3261118</t>
-  </si>
-  <si>
-    <t>OH6635834</t>
-  </si>
-  <si>
-    <t>OH6635835</t>
-  </si>
-  <si>
-    <t>OH6635836</t>
-  </si>
-  <si>
-    <t>OH6635837</t>
-  </si>
-  <si>
-    <t>OH6635838</t>
-  </si>
-  <si>
-    <t>OH6635839</t>
-  </si>
-  <si>
-    <t>OH9450481</t>
-  </si>
-  <si>
-    <t>OH9450482</t>
-  </si>
-  <si>
-    <t>OH9450483</t>
-  </si>
-  <si>
-    <t>OH9450484</t>
-  </si>
-  <si>
-    <t>OH9450485</t>
-  </si>
-  <si>
-    <t>OH9450486</t>
-  </si>
-  <si>
-    <t>OH6116715</t>
-  </si>
-  <si>
-    <t>OH6116716</t>
-  </si>
-  <si>
-    <t>OH6116717</t>
-  </si>
-  <si>
-    <t>OH6116718</t>
-  </si>
-  <si>
-    <t>OH6116719</t>
-  </si>
-  <si>
-    <t>OH6116720</t>
-  </si>
-  <si>
-    <t>IL3858216</t>
-  </si>
-  <si>
-    <t>IL3858217</t>
-  </si>
-  <si>
-    <t>IL3858218</t>
-  </si>
-  <si>
-    <t>IL3858219</t>
-  </si>
-  <si>
-    <t>IL3858220</t>
-  </si>
-  <si>
-    <t>IL3858221</t>
-  </si>
-  <si>
-    <t>GA8190602</t>
-  </si>
-  <si>
-    <t>GA8190603</t>
-  </si>
-  <si>
-    <t>GA8190604</t>
-  </si>
-  <si>
-    <t>GA8190605</t>
-  </si>
-  <si>
-    <t>GA8190606</t>
-  </si>
-  <si>
-    <t>GA8190607</t>
-  </si>
-  <si>
-    <t>IL1895571</t>
-  </si>
-  <si>
-    <t>IL1895572</t>
-  </si>
-  <si>
-    <t>IL1895573</t>
-  </si>
-  <si>
-    <t>IL1895574</t>
-  </si>
-  <si>
-    <t>IL1895575</t>
-  </si>
-  <si>
-    <t>IL1895576</t>
+    <t>OH0000076</t>
+  </si>
+  <si>
+    <t>OH0000077</t>
+  </si>
+  <si>
+    <t>OH0000078</t>
+  </si>
+  <si>
+    <t>OH0000079</t>
+  </si>
+  <si>
+    <t>OH0000080</t>
+  </si>
+  <si>
+    <t>OH0000081</t>
+  </si>
+  <si>
+    <t>IL0000042</t>
+  </si>
+  <si>
+    <t>IL0000043</t>
+  </si>
+  <si>
+    <t>IL0000044</t>
+  </si>
+  <si>
+    <t>IL0000045</t>
+  </si>
+  <si>
+    <t>IL0000046</t>
+  </si>
+  <si>
+    <t>IL0000047</t>
+  </si>
+  <si>
+    <t>GA0000014</t>
+  </si>
+  <si>
+    <t>GA0000015</t>
+  </si>
+  <si>
+    <t>GA0000016</t>
+  </si>
+  <si>
+    <t>GA0000017</t>
+  </si>
+  <si>
+    <t>GA0000018</t>
+  </si>
+  <si>
+    <t>GA0000019</t>
+  </si>
+  <si>
+    <t>OH0000131</t>
+  </si>
+  <si>
+    <t>OH0000132</t>
+  </si>
+  <si>
+    <t>OH0000133</t>
+  </si>
+  <si>
+    <t>OH0000134</t>
+  </si>
+  <si>
+    <t>OH0000135</t>
+  </si>
+  <si>
+    <t>OH0000136</t>
+  </si>
+  <si>
+    <t>OH0000085</t>
+  </si>
+  <si>
+    <t>OH0000086</t>
+  </si>
+  <si>
+    <t>OH0000087</t>
+  </si>
+  <si>
+    <t>OH0000088</t>
+  </si>
+  <si>
+    <t>OH0000089</t>
+  </si>
+  <si>
+    <t>OH0000090</t>
+  </si>
+  <si>
+    <t>TX0000159</t>
+  </si>
+  <si>
+    <t>TX0000160</t>
+  </si>
+  <si>
+    <t>TX0000161</t>
+  </si>
+  <si>
+    <t>TX0000162</t>
+  </si>
+  <si>
+    <t>TX0000163</t>
+  </si>
+  <si>
+    <t>TX0000164</t>
+  </si>
+  <si>
+    <t>OH0000113</t>
+  </si>
+  <si>
+    <t>OH0000114</t>
+  </si>
+  <si>
+    <t>OH0000115</t>
+  </si>
+  <si>
+    <t>OH0000116</t>
+  </si>
+  <si>
+    <t>OH0000117</t>
+  </si>
+  <si>
+    <t>OH0000118</t>
+  </si>
+  <si>
+    <t>OH0000142</t>
+  </si>
+  <si>
+    <t>OH0000143</t>
+  </si>
+  <si>
+    <t>OH0000144</t>
+  </si>
+  <si>
+    <t>OH0000145</t>
+  </si>
+  <si>
+    <t>OH0000146</t>
+  </si>
+  <si>
+    <t>OH0000147</t>
+  </si>
+  <si>
+    <t>OH0000105</t>
+  </si>
+  <si>
+    <t>OH0000106</t>
+  </si>
+  <si>
+    <t>OH0000107</t>
+  </si>
+  <si>
+    <t>OH0000108</t>
+  </si>
+  <si>
+    <t>OH0000109</t>
+  </si>
+  <si>
+    <t>OH0000110</t>
+  </si>
+  <si>
+    <t>IL0000050</t>
+  </si>
+  <si>
+    <t>IL0000051</t>
+  </si>
+  <si>
+    <t>IL0000052</t>
+  </si>
+  <si>
+    <t>IL0000053</t>
+  </si>
+  <si>
+    <t>IL0000054</t>
+  </si>
+  <si>
+    <t>IL0000055</t>
+  </si>
+  <si>
+    <t>GA0000021</t>
+  </si>
+  <si>
+    <t>GA0000022</t>
+  </si>
+  <si>
+    <t>GA0000023</t>
+  </si>
+  <si>
+    <t>GA0000024</t>
+  </si>
+  <si>
+    <t>GA0000025</t>
+  </si>
+  <si>
+    <t>GA0000026</t>
+  </si>
+  <si>
+    <t>IL0000031</t>
+  </si>
+  <si>
+    <t>IL0000032</t>
+  </si>
+  <si>
+    <t>IL0000033</t>
+  </si>
+  <si>
+    <t>IL0000034</t>
+  </si>
+  <si>
+    <t>IL0000035</t>
+  </si>
+  <si>
+    <t>IL0000036</t>
   </si>
   <si>
     <t>CDL Holder</t>
   </si>
   <si>
-    <t>(614) 821-5212</t>
-  </si>
-  <si>
-    <t>(312) 284-7914</t>
-  </si>
-  <si>
-    <t>(404) 720-5860</t>
-  </si>
-  <si>
-    <t>(614) 897-8705</t>
-  </si>
-  <si>
-    <t>(614) 806-7535</t>
-  </si>
-  <si>
-    <t>(512) 621-2178</t>
-  </si>
-  <si>
-    <t>(614) 574-7480</t>
-  </si>
-  <si>
-    <t>(614) 937-6329</t>
-  </si>
-  <si>
-    <t>(614) 935-8132</t>
-  </si>
-  <si>
-    <t>(312) 807-8788</t>
-  </si>
-  <si>
-    <t>(404) 231-4428</t>
-  </si>
-  <si>
-    <t>(312) 300-1431</t>
+    <t>(614) 555-0107</t>
+  </si>
+  <si>
+    <t>(312) 555-0101</t>
+  </si>
+  <si>
+    <t>(404) 555-0107</t>
+  </si>
+  <si>
+    <t>(614) 555-0111</t>
+  </si>
+  <si>
+    <t>(614) 555-0106</t>
+  </si>
+  <si>
+    <t>(512) 555-0100</t>
+  </si>
+  <si>
+    <t>(614) 555-0105</t>
+  </si>
+  <si>
+    <t>(614) 555-0114</t>
+  </si>
+  <si>
+    <t>(614) 555-0113</t>
+  </si>
+  <si>
+    <t>(312) 555-0109</t>
+  </si>
+  <si>
+    <t>(404) 555-0100</t>
+  </si>
+  <si>
+    <t>(312) 555-0103</t>
   </si>
   <si>
     <t>OH-ME-970443</t>
@@ -1844,40 +1844,40 @@
     <t>BOF Fleet Safety &amp; Compliance Policy 2024</t>
   </si>
   <si>
-    <t>DRV-001    322-40-9443</t>
-  </si>
-  <si>
-    <t>DRV-002    164-67-3407</t>
-  </si>
-  <si>
-    <t>DRV-003    997-32-7047</t>
-  </si>
-  <si>
-    <t>DRV-004    136-33-8257</t>
-  </si>
-  <si>
-    <t>DRV-005    438-27-1789</t>
-  </si>
-  <si>
-    <t>DRV-006    121-25-1521</t>
-  </si>
-  <si>
-    <t>DRV-007    560-64-4815</t>
-  </si>
-  <si>
-    <t>DRV-008    441-80-4800</t>
-  </si>
-  <si>
-    <t>DRV-009    876-90-9930</t>
-  </si>
-  <si>
-    <t>DRV-010    609-69-5590</t>
-  </si>
-  <si>
-    <t>DRV-011    389-76-5273</t>
-  </si>
-  <si>
-    <t>DRV-012    815-21-5664</t>
+    <t>DRV-001    900-00-0123</t>
+  </si>
+  <si>
+    <t>DRV-002    900-00-0105</t>
+  </si>
+  <si>
+    <t>DRV-003    900-00-0116</t>
+  </si>
+  <si>
+    <t>DRV-004    900-00-0119</t>
+  </si>
+  <si>
+    <t>DRV-005    900-00-0102</t>
+  </si>
+  <si>
+    <t>DRV-006    900-00-0101</t>
+  </si>
+  <si>
+    <t>DRV-007    900-00-0109</t>
+  </si>
+  <si>
+    <t>DRV-008    900-00-0108</t>
+  </si>
+  <si>
+    <t>DRV-009    900-00-0124</t>
+  </si>
+  <si>
+    <t>DRV-010    900-00-0112</t>
+  </si>
+  <si>
+    <t>DRV-011    900-00-0111</t>
+  </si>
+  <si>
+    <t>DRV-012    900-00-0114</t>
   </si>
   <si>
     <t>John T. Carter</t>
@@ -2714,10 +2714,10 @@
         <v>192</v>
       </c>
       <c r="G2">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H2">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I2" t="s">
         <v>197</v>
@@ -2753,7 +2753,7 @@
         <v>310</v>
       </c>
       <c r="U2" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V2" t="s">
         <v>312</v>
@@ -3076,10 +3076,10 @@
         <v>192</v>
       </c>
       <c r="G3">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H3">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I3" t="s">
         <v>198</v>
@@ -3115,7 +3115,7 @@
         <v>310</v>
       </c>
       <c r="U3" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V3" t="s">
         <v>312</v>
@@ -3438,10 +3438,10 @@
         <v>192</v>
       </c>
       <c r="G4">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H4">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I4" t="s">
         <v>199</v>
@@ -3477,7 +3477,7 @@
         <v>310</v>
       </c>
       <c r="U4" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V4" t="s">
         <v>312</v>
@@ -3800,10 +3800,10 @@
         <v>192</v>
       </c>
       <c r="G5">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H5">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I5" t="s">
         <v>200</v>
@@ -3839,7 +3839,7 @@
         <v>310</v>
       </c>
       <c r="U5" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V5" t="s">
         <v>312</v>
@@ -4162,10 +4162,10 @@
         <v>192</v>
       </c>
       <c r="G6">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H6">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I6" t="s">
         <v>201</v>
@@ -4201,7 +4201,7 @@
         <v>310</v>
       </c>
       <c r="U6" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V6" t="s">
         <v>312</v>
@@ -4524,10 +4524,10 @@
         <v>192</v>
       </c>
       <c r="G7">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H7">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I7" t="s">
         <v>202</v>
@@ -4566,7 +4566,7 @@
         <v>310</v>
       </c>
       <c r="U7" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V7" t="s">
         <v>312</v>
@@ -4889,10 +4889,10 @@
         <v>192</v>
       </c>
       <c r="G8">
-        <v>423877480</v>
+        <v>000000104</v>
       </c>
       <c r="H8">
-        <v>282935636</v>
+        <v>999900202</v>
       </c>
       <c r="I8" t="s">
         <v>203</v>
@@ -4928,7 +4928,7 @@
         <v>310</v>
       </c>
       <c r="U8" s="2">
-        <v>25941</v>
+        <v>25934</v>
       </c>
       <c r="V8" t="s">
         <v>312</v>
@@ -5251,10 +5251,10 @@
         <v>193</v>
       </c>
       <c r="G9">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H9">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I9" t="s">
         <v>197</v>
@@ -5290,7 +5290,7 @@
         <v>311</v>
       </c>
       <c r="U9" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V9" t="s">
         <v>313</v>
@@ -5625,10 +5625,10 @@
         <v>193</v>
       </c>
       <c r="G10">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H10">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I10" t="s">
         <v>198</v>
@@ -5664,7 +5664,7 @@
         <v>311</v>
       </c>
       <c r="U10" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V10" t="s">
         <v>313</v>
@@ -5999,10 +5999,10 @@
         <v>193</v>
       </c>
       <c r="G11">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H11">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I11" t="s">
         <v>199</v>
@@ -6038,7 +6038,7 @@
         <v>311</v>
       </c>
       <c r="U11" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V11" t="s">
         <v>313</v>
@@ -6373,10 +6373,10 @@
         <v>193</v>
       </c>
       <c r="G12">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H12">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I12" t="s">
         <v>200</v>
@@ -6412,7 +6412,7 @@
         <v>311</v>
       </c>
       <c r="U12" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V12" t="s">
         <v>313</v>
@@ -6747,10 +6747,10 @@
         <v>193</v>
       </c>
       <c r="G13">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H13">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I13" t="s">
         <v>201</v>
@@ -6786,7 +6786,7 @@
         <v>311</v>
       </c>
       <c r="U13" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V13" t="s">
         <v>313</v>
@@ -7121,10 +7121,10 @@
         <v>193</v>
       </c>
       <c r="G14">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H14">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I14" t="s">
         <v>202</v>
@@ -7163,7 +7163,7 @@
         <v>311</v>
       </c>
       <c r="U14" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V14" t="s">
         <v>313</v>
@@ -7498,10 +7498,10 @@
         <v>193</v>
       </c>
       <c r="G15">
-        <v>465266204</v>
+        <v>000000107</v>
       </c>
       <c r="H15">
-        <v>102381328</v>
+        <v>999900201</v>
       </c>
       <c r="I15" t="s">
         <v>203</v>
@@ -7537,7 +7537,7 @@
         <v>311</v>
       </c>
       <c r="U15" s="2">
-        <v>30320</v>
+        <v>30317</v>
       </c>
       <c r="V15" t="s">
         <v>313</v>
@@ -7872,10 +7872,10 @@
         <v>193</v>
       </c>
       <c r="G16">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H16">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I16" t="s">
         <v>197</v>
@@ -7911,7 +7911,7 @@
         <v>310</v>
       </c>
       <c r="U16" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V16" t="s">
         <v>314</v>
@@ -8237,10 +8237,10 @@
         <v>193</v>
       </c>
       <c r="G17">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H17">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I17" t="s">
         <v>198</v>
@@ -8276,7 +8276,7 @@
         <v>310</v>
       </c>
       <c r="U17" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V17" t="s">
         <v>314</v>
@@ -8602,10 +8602,10 @@
         <v>193</v>
       </c>
       <c r="G18">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H18">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I18" t="s">
         <v>199</v>
@@ -8641,7 +8641,7 @@
         <v>310</v>
       </c>
       <c r="U18" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V18" t="s">
         <v>314</v>
@@ -8967,10 +8967,10 @@
         <v>193</v>
       </c>
       <c r="G19">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H19">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I19" t="s">
         <v>200</v>
@@ -9006,7 +9006,7 @@
         <v>310</v>
       </c>
       <c r="U19" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V19" t="s">
         <v>314</v>
@@ -9332,10 +9332,10 @@
         <v>193</v>
       </c>
       <c r="G20">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H20">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I20" t="s">
         <v>201</v>
@@ -9371,7 +9371,7 @@
         <v>310</v>
       </c>
       <c r="U20" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V20" t="s">
         <v>314</v>
@@ -9697,10 +9697,10 @@
         <v>193</v>
       </c>
       <c r="G21">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H21">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I21" t="s">
         <v>202</v>
@@ -9739,7 +9739,7 @@
         <v>310</v>
       </c>
       <c r="U21" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V21" t="s">
         <v>314</v>
@@ -10065,10 +10065,10 @@
         <v>193</v>
       </c>
       <c r="G22">
-        <v>942648543</v>
+        <v>000000111</v>
       </c>
       <c r="H22">
-        <v>963584641</v>
+        <v>999900211</v>
       </c>
       <c r="I22" t="s">
         <v>203</v>
@@ -10104,7 +10104,7 @@
         <v>310</v>
       </c>
       <c r="U22" s="2">
-        <v>25937</v>
+        <v>25934</v>
       </c>
       <c r="V22" t="s">
         <v>314</v>
@@ -10430,10 +10430,10 @@
         <v>193</v>
       </c>
       <c r="G23">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H23">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I23" t="s">
         <v>197</v>
@@ -10469,7 +10469,7 @@
         <v>311</v>
       </c>
       <c r="U23" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V23" t="s">
         <v>315</v>
@@ -10801,10 +10801,10 @@
         <v>193</v>
       </c>
       <c r="G24">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H24">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I24" t="s">
         <v>198</v>
@@ -10840,7 +10840,7 @@
         <v>311</v>
       </c>
       <c r="U24" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V24" t="s">
         <v>315</v>
@@ -11172,10 +11172,10 @@
         <v>193</v>
       </c>
       <c r="G25">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H25">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I25" t="s">
         <v>199</v>
@@ -11211,7 +11211,7 @@
         <v>311</v>
       </c>
       <c r="U25" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V25" t="s">
         <v>315</v>
@@ -11543,10 +11543,10 @@
         <v>193</v>
       </c>
       <c r="G26">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H26">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I26" t="s">
         <v>204</v>
@@ -11582,7 +11582,7 @@
         <v>311</v>
       </c>
       <c r="U26" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V26" t="s">
         <v>315</v>
@@ -11914,10 +11914,10 @@
         <v>193</v>
       </c>
       <c r="G27">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H27">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I27" t="s">
         <v>201</v>
@@ -11953,7 +11953,7 @@
         <v>311</v>
       </c>
       <c r="U27" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V27" t="s">
         <v>315</v>
@@ -12285,10 +12285,10 @@
         <v>193</v>
       </c>
       <c r="G28">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H28">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I28" t="s">
         <v>202</v>
@@ -12327,7 +12327,7 @@
         <v>311</v>
       </c>
       <c r="U28" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V28" t="s">
         <v>315</v>
@@ -12659,10 +12659,10 @@
         <v>193</v>
       </c>
       <c r="G29">
-        <v>190070998</v>
+        <v>000000101</v>
       </c>
       <c r="H29">
-        <v>301147109</v>
+        <v>999900203</v>
       </c>
       <c r="I29" t="s">
         <v>203</v>
@@ -12698,7 +12698,7 @@
         <v>311</v>
       </c>
       <c r="U29" s="2">
-        <v>34193</v>
+        <v>33970</v>
       </c>
       <c r="V29" t="s">
         <v>315</v>
@@ -13030,10 +13030,10 @@
         <v>193</v>
       </c>
       <c r="G30">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H30">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I30" t="s">
         <v>197</v>
@@ -13069,7 +13069,7 @@
         <v>310</v>
       </c>
       <c r="U30" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V30" t="s">
         <v>316</v>
@@ -13404,10 +13404,10 @@
         <v>193</v>
       </c>
       <c r="G31">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H31">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I31" t="s">
         <v>198</v>
@@ -13443,7 +13443,7 @@
         <v>310</v>
       </c>
       <c r="U31" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V31" t="s">
         <v>316</v>
@@ -13778,10 +13778,10 @@
         <v>193</v>
       </c>
       <c r="G32">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H32">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I32" t="s">
         <v>199</v>
@@ -13817,7 +13817,7 @@
         <v>310</v>
       </c>
       <c r="U32" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V32" t="s">
         <v>316</v>
@@ -14152,10 +14152,10 @@
         <v>193</v>
       </c>
       <c r="G33">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H33">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I33" t="s">
         <v>200</v>
@@ -14191,7 +14191,7 @@
         <v>310</v>
       </c>
       <c r="U33" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V33" t="s">
         <v>316</v>
@@ -14526,10 +14526,10 @@
         <v>193</v>
       </c>
       <c r="G34">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H34">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I34" t="s">
         <v>201</v>
@@ -14565,7 +14565,7 @@
         <v>310</v>
       </c>
       <c r="U34" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V34" t="s">
         <v>316</v>
@@ -14900,10 +14900,10 @@
         <v>193</v>
       </c>
       <c r="G35">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H35">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I35" t="s">
         <v>202</v>
@@ -14942,7 +14942,7 @@
         <v>310</v>
       </c>
       <c r="U35" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V35" t="s">
         <v>316</v>
@@ -15277,10 +15277,10 @@
         <v>193</v>
       </c>
       <c r="G36">
-        <v>426693965</v>
+        <v>000000105</v>
       </c>
       <c r="H36">
-        <v>701598966</v>
+        <v>999900206</v>
       </c>
       <c r="I36" t="s">
         <v>203</v>
@@ -15316,7 +15316,7 @@
         <v>310</v>
       </c>
       <c r="U36" s="2">
-        <v>24398</v>
+        <v>24108</v>
       </c>
       <c r="V36" t="s">
         <v>316</v>
@@ -15651,10 +15651,10 @@
         <v>193</v>
       </c>
       <c r="G37">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H37">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I37" t="s">
         <v>197</v>
@@ -15690,7 +15690,7 @@
         <v>310</v>
       </c>
       <c r="U37" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V37" t="s">
         <v>317</v>
@@ -16016,10 +16016,10 @@
         <v>193</v>
       </c>
       <c r="G38">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H38">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I38" t="s">
         <v>198</v>
@@ -16055,7 +16055,7 @@
         <v>310</v>
       </c>
       <c r="U38" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V38" t="s">
         <v>317</v>
@@ -16381,10 +16381,10 @@
         <v>193</v>
       </c>
       <c r="G39">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H39">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I39" t="s">
         <v>199</v>
@@ -16420,7 +16420,7 @@
         <v>310</v>
       </c>
       <c r="U39" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V39" t="s">
         <v>317</v>
@@ -16746,10 +16746,10 @@
         <v>193</v>
       </c>
       <c r="G40">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H40">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I40" t="s">
         <v>200</v>
@@ -16785,7 +16785,7 @@
         <v>310</v>
       </c>
       <c r="U40" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V40" t="s">
         <v>317</v>
@@ -17111,10 +17111,10 @@
         <v>193</v>
       </c>
       <c r="G41">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H41">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I41" t="s">
         <v>201</v>
@@ -17150,7 +17150,7 @@
         <v>310</v>
       </c>
       <c r="U41" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V41" t="s">
         <v>317</v>
@@ -17476,10 +17476,10 @@
         <v>193</v>
       </c>
       <c r="G42">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H42">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I42" t="s">
         <v>202</v>
@@ -17518,7 +17518,7 @@
         <v>310</v>
       </c>
       <c r="U42" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V42" t="s">
         <v>317</v>
@@ -17844,10 +17844,10 @@
         <v>193</v>
       </c>
       <c r="G43">
-        <v>973738233</v>
+        <v>000000112</v>
       </c>
       <c r="H43">
-        <v>771220803</v>
+        <v>999900207</v>
       </c>
       <c r="I43" t="s">
         <v>203</v>
@@ -17883,7 +17883,7 @@
         <v>310</v>
       </c>
       <c r="U43" s="2">
-        <v>25607</v>
+        <v>25569</v>
       </c>
       <c r="V43" t="s">
         <v>317</v>
@@ -18209,10 +18209,10 @@
         <v>194</v>
       </c>
       <c r="G44">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H44">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I44" t="s">
         <v>197</v>
@@ -18248,7 +18248,7 @@
         <v>311</v>
       </c>
       <c r="U44" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V44" t="s">
         <v>318</v>
@@ -18568,10 +18568,10 @@
         <v>194</v>
       </c>
       <c r="G45">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H45">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I45" t="s">
         <v>198</v>
@@ -18607,7 +18607,7 @@
         <v>311</v>
       </c>
       <c r="U45" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V45" t="s">
         <v>318</v>
@@ -18927,10 +18927,10 @@
         <v>194</v>
       </c>
       <c r="G46">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H46">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I46" t="s">
         <v>199</v>
@@ -18966,7 +18966,7 @@
         <v>311</v>
       </c>
       <c r="U46" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V46" t="s">
         <v>318</v>
@@ -19286,10 +19286,10 @@
         <v>194</v>
       </c>
       <c r="G47">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H47">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I47" t="s">
         <v>200</v>
@@ -19325,7 +19325,7 @@
         <v>311</v>
       </c>
       <c r="U47" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V47" t="s">
         <v>318</v>
@@ -19645,10 +19645,10 @@
         <v>194</v>
       </c>
       <c r="G48">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H48">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I48" t="s">
         <v>201</v>
@@ -19684,7 +19684,7 @@
         <v>311</v>
       </c>
       <c r="U48" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V48" t="s">
         <v>318</v>
@@ -20004,10 +20004,10 @@
         <v>194</v>
       </c>
       <c r="G49">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H49">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I49" t="s">
         <v>202</v>
@@ -20046,7 +20046,7 @@
         <v>311</v>
       </c>
       <c r="U49" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V49" t="s">
         <v>318</v>
@@ -20366,10 +20366,10 @@
         <v>194</v>
       </c>
       <c r="G50">
-        <v>865581806</v>
+        <v>000000110</v>
       </c>
       <c r="H50">
-        <v>994359424</v>
+        <v>999900212</v>
       </c>
       <c r="I50" t="s">
         <v>203</v>
@@ -20405,7 +20405,7 @@
         <v>311</v>
       </c>
       <c r="U50" s="2">
-        <v>36508</v>
+        <v>36161</v>
       </c>
       <c r="V50" t="s">
         <v>318</v>
@@ -20725,10 +20725,10 @@
         <v>195</v>
       </c>
       <c r="G51">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H51">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I51" t="s">
         <v>197</v>
@@ -20764,7 +20764,7 @@
         <v>310</v>
       </c>
       <c r="U51" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V51" t="s">
         <v>319</v>
@@ -21099,10 +21099,10 @@
         <v>195</v>
       </c>
       <c r="G52">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H52">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I52" t="s">
         <v>198</v>
@@ -21138,7 +21138,7 @@
         <v>310</v>
       </c>
       <c r="U52" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V52" t="s">
         <v>319</v>
@@ -21473,10 +21473,10 @@
         <v>195</v>
       </c>
       <c r="G53">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H53">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I53" t="s">
         <v>199</v>
@@ -21512,7 +21512,7 @@
         <v>310</v>
       </c>
       <c r="U53" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V53" t="s">
         <v>319</v>
@@ -21847,10 +21847,10 @@
         <v>195</v>
       </c>
       <c r="G54">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H54">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I54" t="s">
         <v>200</v>
@@ -21886,7 +21886,7 @@
         <v>310</v>
       </c>
       <c r="U54" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V54" t="s">
         <v>319</v>
@@ -22221,10 +22221,10 @@
         <v>195</v>
       </c>
       <c r="G55">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H55">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I55" t="s">
         <v>201</v>
@@ -22260,7 +22260,7 @@
         <v>310</v>
       </c>
       <c r="U55" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V55" t="s">
         <v>319</v>
@@ -22595,10 +22595,10 @@
         <v>195</v>
       </c>
       <c r="G56">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H56">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I56" t="s">
         <v>202</v>
@@ -22637,7 +22637,7 @@
         <v>310</v>
       </c>
       <c r="U56" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V56" t="s">
         <v>319</v>
@@ -22972,10 +22972,10 @@
         <v>195</v>
       </c>
       <c r="G57">
-        <v>560687670</v>
+        <v>000000108</v>
       </c>
       <c r="H57">
-        <v>455374220</v>
+        <v>999900204</v>
       </c>
       <c r="I57" t="s">
         <v>203</v>
@@ -23011,7 +23011,7 @@
         <v>310</v>
       </c>
       <c r="U57" s="2">
-        <v>23612</v>
+        <v>23377</v>
       </c>
       <c r="V57" t="s">
         <v>319</v>
@@ -23346,10 +23346,10 @@
         <v>193</v>
       </c>
       <c r="G58">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H58">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I58" t="s">
         <v>197</v>
@@ -23385,7 +23385,7 @@
         <v>311</v>
       </c>
       <c r="U58" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V58" t="s">
         <v>320</v>
@@ -23714,10 +23714,10 @@
         <v>193</v>
       </c>
       <c r="G59">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H59">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I59" t="s">
         <v>198</v>
@@ -23753,7 +23753,7 @@
         <v>311</v>
       </c>
       <c r="U59" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V59" t="s">
         <v>320</v>
@@ -24082,10 +24082,10 @@
         <v>193</v>
       </c>
       <c r="G60">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H60">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I60" t="s">
         <v>199</v>
@@ -24121,7 +24121,7 @@
         <v>311</v>
       </c>
       <c r="U60" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V60" t="s">
         <v>320</v>
@@ -24450,10 +24450,10 @@
         <v>193</v>
       </c>
       <c r="G61">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H61">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I61" t="s">
         <v>200</v>
@@ -24489,7 +24489,7 @@
         <v>311</v>
       </c>
       <c r="U61" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V61" t="s">
         <v>320</v>
@@ -24818,10 +24818,10 @@
         <v>193</v>
       </c>
       <c r="G62">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H62">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I62" t="s">
         <v>201</v>
@@ -24857,7 +24857,7 @@
         <v>311</v>
       </c>
       <c r="U62" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V62" t="s">
         <v>320</v>
@@ -25186,10 +25186,10 @@
         <v>193</v>
       </c>
       <c r="G63">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H63">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I63" t="s">
         <v>202</v>
@@ -25228,7 +25228,7 @@
         <v>311</v>
       </c>
       <c r="U63" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V63" t="s">
         <v>320</v>
@@ -25557,10 +25557,10 @@
         <v>193</v>
       </c>
       <c r="G64">
-        <v>347101867</v>
+        <v>000000103</v>
       </c>
       <c r="H64">
-        <v>959838087</v>
+        <v>999900210</v>
       </c>
       <c r="I64" t="s">
         <v>203</v>
@@ -25596,7 +25596,7 @@
         <v>311</v>
       </c>
       <c r="U64" s="2">
-        <v>30971</v>
+        <v>30682</v>
       </c>
       <c r="V64" t="s">
         <v>320</v>
@@ -25925,10 +25925,10 @@
         <v>193</v>
       </c>
       <c r="G65">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H65">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I65" t="s">
         <v>197</v>
@@ -25964,7 +25964,7 @@
         <v>310</v>
       </c>
       <c r="U65" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V65" t="s">
         <v>321</v>
@@ -26287,10 +26287,10 @@
         <v>193</v>
       </c>
       <c r="G66">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H66">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I66" t="s">
         <v>198</v>
@@ -26326,7 +26326,7 @@
         <v>310</v>
       </c>
       <c r="U66" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V66" t="s">
         <v>321</v>
@@ -26649,10 +26649,10 @@
         <v>193</v>
       </c>
       <c r="G67">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H67">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I67" t="s">
         <v>199</v>
@@ -26688,7 +26688,7 @@
         <v>310</v>
       </c>
       <c r="U67" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V67" t="s">
         <v>321</v>
@@ -27011,10 +27011,10 @@
         <v>193</v>
       </c>
       <c r="G68">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H68">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I68" t="s">
         <v>200</v>
@@ -27050,7 +27050,7 @@
         <v>310</v>
       </c>
       <c r="U68" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V68" t="s">
         <v>321</v>
@@ -27373,10 +27373,10 @@
         <v>193</v>
       </c>
       <c r="G69">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H69">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I69" t="s">
         <v>201</v>
@@ -27412,7 +27412,7 @@
         <v>310</v>
       </c>
       <c r="U69" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V69" t="s">
         <v>321</v>
@@ -27735,10 +27735,10 @@
         <v>193</v>
       </c>
       <c r="G70">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H70">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I70" t="s">
         <v>202</v>
@@ -27777,7 +27777,7 @@
         <v>310</v>
       </c>
       <c r="U70" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V70" t="s">
         <v>321</v>
@@ -28100,10 +28100,10 @@
         <v>193</v>
       </c>
       <c r="G71">
-        <v>446897081</v>
+        <v>000000106</v>
       </c>
       <c r="H71">
-        <v>856706839</v>
+        <v>999900208</v>
       </c>
       <c r="I71" t="s">
         <v>203</v>
@@ -28139,7 +28139,7 @@
         <v>310</v>
       </c>
       <c r="U71" s="2">
-        <v>24361</v>
+        <v>24108</v>
       </c>
       <c r="V71" t="s">
         <v>321</v>
@@ -28462,10 +28462,10 @@
         <v>194</v>
       </c>
       <c r="G72">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H72">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I72" t="s">
         <v>197</v>
@@ -28501,7 +28501,7 @@
         <v>311</v>
       </c>
       <c r="U72" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V72" t="s">
         <v>322</v>
@@ -28824,10 +28824,10 @@
         <v>194</v>
       </c>
       <c r="G73">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H73">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I73" t="s">
         <v>198</v>
@@ -28863,7 +28863,7 @@
         <v>311</v>
       </c>
       <c r="U73" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V73" t="s">
         <v>322</v>
@@ -29186,10 +29186,10 @@
         <v>194</v>
       </c>
       <c r="G74">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H74">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I74" t="s">
         <v>199</v>
@@ -29225,7 +29225,7 @@
         <v>311</v>
       </c>
       <c r="U74" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V74" t="s">
         <v>322</v>
@@ -29548,10 +29548,10 @@
         <v>194</v>
       </c>
       <c r="G75">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H75">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I75" t="s">
         <v>200</v>
@@ -29587,7 +29587,7 @@
         <v>311</v>
       </c>
       <c r="U75" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V75" t="s">
         <v>322</v>
@@ -29910,10 +29910,10 @@
         <v>194</v>
       </c>
       <c r="G76">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H76">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I76" t="s">
         <v>201</v>
@@ -29949,7 +29949,7 @@
         <v>311</v>
       </c>
       <c r="U76" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V76" t="s">
         <v>322</v>
@@ -30272,10 +30272,10 @@
         <v>194</v>
       </c>
       <c r="G77">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H77">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I77" t="s">
         <v>202</v>
@@ -30314,7 +30314,7 @@
         <v>311</v>
       </c>
       <c r="U77" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V77" t="s">
         <v>322</v>
@@ -30637,10 +30637,10 @@
         <v>194</v>
       </c>
       <c r="G78">
-        <v>207931918</v>
+        <v>000000102</v>
       </c>
       <c r="H78">
-        <v>906722449</v>
+        <v>999900209</v>
       </c>
       <c r="I78" t="s">
         <v>203</v>
@@ -30676,7 +30676,7 @@
         <v>311</v>
       </c>
       <c r="U78" s="2">
-        <v>24911</v>
+        <v>24838</v>
       </c>
       <c r="V78" t="s">
         <v>322</v>
@@ -30999,10 +30999,10 @@
         <v>196</v>
       </c>
       <c r="G79">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H79">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I79" t="s">
         <v>197</v>
@@ -31038,7 +31038,7 @@
         <v>310</v>
       </c>
       <c r="U79" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V79" t="s">
         <v>323</v>
@@ -31370,10 +31370,10 @@
         <v>196</v>
       </c>
       <c r="G80">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H80">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I80" t="s">
         <v>198</v>
@@ -31409,7 +31409,7 @@
         <v>310</v>
       </c>
       <c r="U80" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V80" t="s">
         <v>323</v>
@@ -31741,10 +31741,10 @@
         <v>196</v>
       </c>
       <c r="G81">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H81">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I81" t="s">
         <v>199</v>
@@ -31780,7 +31780,7 @@
         <v>310</v>
       </c>
       <c r="U81" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V81" t="s">
         <v>323</v>
@@ -32112,10 +32112,10 @@
         <v>196</v>
       </c>
       <c r="G82">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H82">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I82" t="s">
         <v>200</v>
@@ -32151,7 +32151,7 @@
         <v>310</v>
       </c>
       <c r="U82" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V82" t="s">
         <v>323</v>
@@ -32483,10 +32483,10 @@
         <v>196</v>
       </c>
       <c r="G83">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H83">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I83" t="s">
         <v>201</v>
@@ -32522,7 +32522,7 @@
         <v>310</v>
       </c>
       <c r="U83" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V83" t="s">
         <v>323</v>
@@ -32854,10 +32854,10 @@
         <v>196</v>
       </c>
       <c r="G84">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H84">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I84" t="s">
         <v>202</v>
@@ -32896,7 +32896,7 @@
         <v>310</v>
       </c>
       <c r="U84" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V84" t="s">
         <v>323</v>
@@ -33228,10 +33228,10 @@
         <v>196</v>
       </c>
       <c r="G85">
-        <v>782385202</v>
+        <v>000000109</v>
       </c>
       <c r="H85">
-        <v>689231916</v>
+        <v>999900205</v>
       </c>
       <c r="I85" t="s">
         <v>203</v>
@@ -33267,7 +33267,7 @@
         <v>310</v>
       </c>
       <c r="U85" s="2">
-        <v>32974</v>
+        <v>32874</v>
       </c>
       <c r="V85" t="s">
         <v>323</v>
